--- a/test/data/all_data/bpbs_test_warning.xlsx
+++ b/test/data/all_data/bpbs_test_warning.xlsx
@@ -1470,7 +1470,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="204">
   <si>
     <t># ORANGE fields are mandatory. Your submission will fail if any mandatory fields are not completed.</t>
   </si>
@@ -2116,6 +2116,9 @@
   <si>
     <t>Anaerobic</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTB313</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3451,7 @@
         <v>190</v>
       </c>
       <c r="S15" s="23" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="T15" s="23" t="s">
         <v>175</v>
